--- a/artfynd/A 23750-2022 artfynd.xlsx
+++ b/artfynd/A 23750-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23750-2022 artfynd.xlsx
+++ b/artfynd/A 23750-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104230992</v>
+        <v>104230964</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490227.4381762688</v>
+        <v>490283</v>
       </c>
       <c r="R2" t="n">
-        <v>6519871.741618443</v>
+        <v>6519919</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Blommar i vägkanten</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +775,7 @@
         <v>104230965</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490283.2178765107</v>
+        <v>490283</v>
       </c>
       <c r="R3" t="n">
-        <v>6519977.765164631</v>
+        <v>6519978</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +840,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104230964</v>
+        <v>104230992</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490283.0721607288</v>
+        <v>490228</v>
       </c>
       <c r="R4" t="n">
-        <v>6519919.764052529</v>
+        <v>6519872</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,22 +939,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Blommar i vägkanten</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23750-2022 artfynd.xlsx
+++ b/artfynd/A 23750-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,8 +988,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>